--- a/howTo26/How2$ production.xlsx
+++ b/howTo26/How2$ production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4E6FEE-4BDF-8A40-86C1-D6D13F0AA2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CA5CE7-6104-E848-9235-7B80D0D838CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4040" yWindow="600" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
+    <workbookView xWindow="10400" yWindow="600" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>

--- a/howTo26/How2$ production.xlsx
+++ b/howTo26/How2$ production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CA5CE7-6104-E848-9235-7B80D0D838CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C11AC44-3EA9-EB44-88C4-CDFFD108668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10400" yWindow="600" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
+    <workbookView xWindow="1520" yWindow="1580" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="190">
   <si>
     <t xml:space="preserve">EMERGENCY CONTACT </t>
   </si>
@@ -295,12 +295,6 @@
   </si>
   <si>
     <t>Grace Albert</t>
-  </si>
-  <si>
-    <t>Laura Hull</t>
-  </si>
-  <si>
-    <t>lmarkow07@gmail.com</t>
   </si>
   <si>
     <t>Bill</t>
@@ -1342,7 +1336,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1372,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="5"/>
@@ -1462,7 +1456,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H5" s="25">
         <v>3</v>
@@ -1648,10 +1642,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C13" s="5">
         <v>6107317668</v>
@@ -1662,7 +1656,7 @@
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H13" s="25">
         <v>11</v>
@@ -1731,7 +1725,7 @@
         <v>6106629204</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E16" s="11">
         <v>3034948820</v>
@@ -1740,7 +1734,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H16" s="30">
         <v>14</v>
@@ -1766,7 +1760,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H17" s="25">
         <v>14</v>
@@ -1818,7 +1812,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H19" s="25">
         <v>17</v>
@@ -1832,7 +1826,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>23</v>
@@ -1844,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H20" s="25">
         <v>18</v>
@@ -1870,7 +1864,7 @@
         <v>3</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H21" s="25">
         <v>19</v>
@@ -1896,48 +1890,52 @@
         <v>3</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H22" s="25">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
-        <v>87</v>
+      <c r="A23" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="11">
-        <v>6106270433</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C23" s="13">
+        <v>6102914298</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="9"/>
       <c r="G23" s="10" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="H23" s="25">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
-        <v>61</v>
+    <row r="24" spans="1:8" ht="26" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C24" s="13">
-        <v>6102914298</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10" t="s">
+        <v>2158963528</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="11">
+        <v>6107169026</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="16" t="s">
         <v>187</v>
       </c>
       <c r="H24" s="25">
@@ -1946,130 +1944,113 @@
     </row>
     <row r="25" spans="1:8" ht="26" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C25" s="13">
-        <v>2158963528</v>
+        <v>4844375278</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E25" s="11">
-        <v>6107169026</v>
+        <v>6107048442</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H25" s="25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="13">
-        <v>4844375278</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="11">
-        <v>6107048442</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="25">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="7"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="9"/>
+      <c r="A27" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="20"/>
       <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="18"/>
+    <row r="28" spans="1:8" ht="26" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="18">
+        <v>2158406582</v>
+      </c>
       <c r="D28" s="10"/>
       <c r="E28" s="18"/>
       <c r="F28" s="20"/>
-      <c r="G28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="26" x14ac:dyDescent="0.2">
+      <c r="G28" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="C29" s="18">
-        <v>2158406582</v>
+        <v>2679344650</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="18"/>
       <c r="F29" s="20"/>
       <c r="G29" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C30" s="18">
-        <v>2679344650</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="18"/>
+        <v>6105470348</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="18">
+        <v>61030809876</v>
+      </c>
       <c r="F30" s="20"/>
       <c r="G30" s="10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="18">
-        <v>6105470348</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="18">
-        <v>61030809876</v>
-      </c>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="18"/>
       <c r="F31" s="20"/>
-      <c r="G31" s="10" t="s">
-        <v>89</v>
-      </c>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="10"/>
@@ -2112,7 +2093,7 @@
       <c r="B36" s="10"/>
       <c r="C36" s="18"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="18"/>
+      <c r="E36" s="10"/>
       <c r="F36" s="20"/>
       <c r="G36" s="10"/>
     </row>
@@ -2128,7 +2109,7 @@
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="18"/>
+      <c r="C38" s="20"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="20"/>
@@ -2144,26 +2125,17 @@
       <c r="G39" s="10"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="10"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="26"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="26"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:H26">
-    <sortCondition ref="H20:H26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:H25">
+    <sortCondition ref="H20:H25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="91" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -2188,25 +2160,25 @@
   <sheetData>
     <row r="1" spans="1:8" s="31" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>129</v>
-      </c>
       <c r="H1" s="35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -2215,7 +2187,7 @@
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" s="43">
         <v>1</v>
@@ -2224,16 +2196,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H3" s="46" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
@@ -2245,16 +2217,16 @@
         <v>2</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2266,13 +2238,13 @@
         <v>13</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2284,59 +2256,59 @@
         <v>22</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E6" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>139</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="B7" s="43" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C7" s="43">
         <v>22</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="B8" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="43">
         <v>23</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2345,16 +2317,16 @@
         <v>33</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H9" s="46"/>
     </row>
@@ -2367,10 +2339,10 @@
         <v>38</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2382,17 +2354,17 @@
         <v>40</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="54"/>
       <c r="H11" s="46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2404,16 +2376,16 @@
         <v>45</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H12" s="51" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2425,16 +2397,16 @@
         <v>56</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2446,16 +2418,16 @@
         <v>64</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G14" s="56" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -2467,16 +2439,16 @@
         <v>68</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2488,19 +2460,19 @@
         <v>69</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2512,16 +2484,16 @@
         <v>72</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H17" s="42" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -2533,13 +2505,13 @@
         <v>76</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2551,16 +2523,16 @@
         <v>79</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2577,7 +2549,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="36" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B22" s="43">
         <v>1</v>
@@ -2586,16 +2558,16 @@
         <v>93</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H22" s="52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2607,16 +2579,16 @@
         <v>99</v>
       </c>
       <c r="D23" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="46" t="s">
         <v>160</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" s="46" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2628,13 +2600,13 @@
         <v>105</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="47" customFormat="1" ht="28" x14ac:dyDescent="0.2">
@@ -2646,17 +2618,17 @@
         <v>111</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="47" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H25" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -2668,16 +2640,16 @@
         <v>115</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H26" s="40"/>
     </row>
@@ -2690,19 +2662,19 @@
         <v>125</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G27" s="40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2714,16 +2686,16 @@
         <v>128</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -2735,13 +2707,13 @@
         <v>133</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2753,30 +2725,30 @@
         <v>134</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B31" s="43" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C31" s="43">
         <v>143</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H31" s="46"/>
     </row>
@@ -2789,16 +2761,16 @@
         <v>143</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F32" s="40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">

--- a/howTo26/How2$ production.xlsx
+++ b/howTo26/How2$ production.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C11AC44-3EA9-EB44-88C4-CDFFD108668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92565AEA-86EB-F84C-B745-33A025BC2965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1580" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
+    <workbookView xWindow="1520" yWindow="1000" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
     <sheet name="Scenes" sheetId="2" r:id="rId2"/>
+    <sheet name="Book Voice" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="236">
   <si>
     <t xml:space="preserve">EMERGENCY CONTACT </t>
   </si>
@@ -381,9 +382,6 @@
     <t>Mailroom</t>
   </si>
   <si>
-    <t>Secretary is Not a Toy</t>
-  </si>
-  <si>
     <t>Same</t>
   </si>
   <si>
@@ -394,9 +392,6 @@
   </si>
   <si>
     <t>fencing and plants</t>
-  </si>
-  <si>
-    <t>Paris Original</t>
   </si>
   <si>
     <t xml:space="preserve">clear terrance </t>
@@ -454,11 +449,6 @@
     <t>Outer office</t>
   </si>
   <si>
-    <t>- The Company Way
-- The Company Way (Reprise)
-- Rosemary's Philosophy</t>
-  </si>
-  <si>
     <t>Traveler</t>
   </si>
   <si>
@@ -508,10 +498,6 @@
   </si>
   <si>
     <t>Elevator landing</t>
-  </si>
-  <si>
-    <t>- Been a Long Day
-- Been a Long Day (Reprise)</t>
   </si>
   <si>
     <t>- Grand Old Ivy
@@ -580,15 +566,6 @@
   </si>
   <si>
     <t>Corridor</t>
-  </si>
-  <si>
-    <t>9a</t>
-  </si>
-  <si>
-    <t>4a</t>
-  </si>
-  <si>
-    <t>4b</t>
   </si>
   <si>
     <t>Office is stage right in front of Biggley's office.  Desk &amp; chair</t>
@@ -645,56 +622,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Paris Original</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> continues</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- Rosemary
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Finale Act One</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">- </t>
     </r>
     <r>
@@ -746,6 +673,228 @@
   <si>
     <t>Scrubwomen 'cleaning up'</t>
   </si>
+  <si>
+    <t>Book Voice Scenes</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dear Reader, This little book is designed to tell you everything you need to know about the science of getting ahead.
+(FINCH turns front toward the audience, and turns page in the book.)
+Now let us assume you are young, healthy, clear-eyed and eager, anxious to rise quickly and easily to the top of the business world. You can!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Finch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: I can!
+If you have education and intelligence and ability, so much the better. But remember</t>
+    </r>
+  </si>
+  <si>
+    <t>How to choose the right company. Before applying for a job, make sure you have chosen the right company. It is essential that the company be a big one. It should be at least big enough so that nobody knows exactly what anyone else is doing.</t>
+  </si>
+  <si>
+    <t>You have alertly seized your opportunities and are now on the first rung of the ladder. You are working in the mailroom. One word of caution about the mailroom: It is a place out of which you must get. Some of your rivals will not have the advantage of this knowledge, but you are forearmed. Do not get stuck in the mailroom. Plan to rise.</t>
+  </si>
+  <si>
+    <t>If you have followed the simple instructions exactly as outlined, you should by now be a junior executive. Congratulations. Nothing can stop you now.</t>
+  </si>
+  <si>
+    <t>Choosing a secretary can be fraught with peril. Take a good look at the young lady who has been assigned to you.
+(BOOK VOICE stops. FINCH looks at HEDY, who is fixing her stocking. FINCH
+begins to read again. BOOK VOICE resumes.)
+If she is so attractive that you feel things are too good to be true, be very careful. It may be that one of the big men in the company is Interested-In-Her-Career. There is a simple test for this. Check on her secretarial skill. The smaller her abilities, the bigger her Protector.</t>
+  </si>
+  <si>
+    <t>So you are now a vice president. You have climbed the ladder of success rung, by painful rung, until you have almost reached the top. You have done beautifully. Unless you are vice president in charge of advertising. In that case you are in terrible trouble. There is only one thing that can save you. You must get. a brilliant idea. The quickest way to get ideas is to develop them. That is, you must examine the undeveloped, worthless notions of others and add to them that extra something that makes the idea your own. An undeveloped notion may come from the least likely source. Be alert! You never know who will bring it to you.</t>
+  </si>
+  <si>
+    <t>The farmer spends his time in the fields, the laborer at his machine, and the businessman at meetings.</t>
+  </si>
+  <si>
+    <t>How to Handle a Disaster.
+— 
+In every business man’s career, there are times when things go a bit wrong. We have many suggestions for coping with these little problems. However, should you be the cause of a disaster that’s really disastrous, we suggest that your best bet is to review the first chapter of this book, How To Apply For A Job.</t>
+  </si>
+  <si>
+    <t>SMITTY / MISS JONES / BUD / MAN / MISS KRUMHOLTZ / ROSEMARY / GIRLS / BOOK VOICE / GATCH / FINCH/ Ensemble</t>
+  </si>
+  <si>
+    <t>SMITTY / BUD / JOHNSON / TACKABERRY / BRATT / ROSEMARY / FINCH / J.B. BIGGLEY / MATTHEWS / BOOK VOICE / JENKINS / PETERSON / GATCH / Ensemble</t>
+  </si>
+  <si>
+    <t>BUD</t>
+  </si>
+  <si>
+    <t>MISS JONES / J.B. BIGGLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The Company Way
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMBALE / BUD / FINCH / TWIMBLE
+(Bill &amp; Marc)
+BRATT
+</t>
+  </si>
+  <si>
+    <t>- The Company Way (Reprise)</t>
+  </si>
+  <si>
+    <t>- Rosemary's Philosophy</t>
+  </si>
+  <si>
+    <t>BUD / FINCH / BRATT / TWIMBLE / Ensemble
+ROSEMARY / FINCH / GATCH</t>
+  </si>
+  <si>
+    <t>ROSEMARY / FINCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Secretary is Not a Toy</t>
+  </si>
+  <si>
+    <t>BUD / HEDY LARUE /BRATT / SMITTY / MISS KRUMHOLTZ  / DAVIS / JENKINS</t>
+  </si>
+  <si>
+    <t>BRATT / JENKINS / BUD / Ensemble</t>
+  </si>
+  <si>
+    <t>Ensemble / MISS KRUMHOLTZ / BIGGLEY / MISS JONES / TACKABERRY / FINCH / ROSEMARY / SMITTY</t>
+  </si>
+  <si>
+    <t>- Been a Long Day</t>
+  </si>
+  <si>
+    <t>- Been a Long Day (Reprise)</t>
+  </si>
+  <si>
+    <t>FINCH / ROSEMARY / SMITTY / Ensemble</t>
+  </si>
+  <si>
+    <t>BIGGLEY / HEDY / BUD</t>
+  </si>
+  <si>
+    <t>BIGGLEY / FINCH / SCRUBWOMEN</t>
+  </si>
+  <si>
+    <t>ROSEMARY / FINCH / HEDY / BIGGLEY</t>
+  </si>
+  <si>
+    <t>MISS KRUMHOLTZ / HEDY / FINCH / GATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRATT / JENKINS / TACKABERRY / ROSEMARY / SMITTY / </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Paris Original</t>
+  </si>
+  <si>
+    <t>ROSEMARY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Paris Original</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> continues</t>
+    </r>
+  </si>
+  <si>
+    <t>ROSEMARY / MISS KRUMHOLTZ / MISS JONES / Ensemble / BUD / HEDY / BIGGLEY / OVINGTON / BRATT</t>
+  </si>
+  <si>
+    <t>HEDY / BUD / Man (Marc) / FINCH</t>
+  </si>
+  <si>
+    <t>HEDY / FINCH</t>
+  </si>
+  <si>
+    <t>HEDY / FINCH / ROSEMARY / BIGGLEY / OVINGTON</t>
+  </si>
+  <si>
+    <t>- Rip the Chipmunk</t>
+  </si>
+  <si>
+    <t>BIGGLEY / OVINGTON / FINCH / BRATT</t>
+  </si>
+  <si>
+    <t>- Rosemary</t>
+  </si>
+  <si>
+    <t>- Finale Act One</t>
+  </si>
+  <si>
+    <t>BUD / FINCH / ROSEMARY</t>
+  </si>
+  <si>
+    <t>SMITTY / BUD / JENKINS / TOYNBEE / BRATT / TACKABERRY / MISS KRUMHOLTZ / ROSEMARY / WOMEN</t>
+  </si>
+  <si>
+    <t>FINCH / ROSEMARY / BUD</t>
+  </si>
+  <si>
+    <t>BUD / FINCH / HEDY / BIGGLEY</t>
+  </si>
+  <si>
+    <t>TACKABERRY / BUD / JENKINS / DAVIS / TOYNBEE / BRATT / FINCH</t>
+  </si>
+  <si>
+    <t>BUD / FINCH / TACKABERRY / BRATT / TOYNBEE / BIGGLEY / DAVIS / JENKINS / MEN</t>
+  </si>
+  <si>
+    <t>BRATT / FINCH / HEDY / TV ANNOUNCER / TACKABERRY / BIGGLEY / Ensemble</t>
+  </si>
+  <si>
+    <t>JENKINS / FINCH / MISS JONES / MEN / BUD / DAVIS / ROSEMARY / TACKABERRY / TOYNBEE / POLICEMAN</t>
+  </si>
+  <si>
+    <t>BUD / FINCH / FOUR MEN</t>
+  </si>
+  <si>
+    <t>EXECUTIVES / J.B. BIGGLEY / FINCH / MEN / WOMPER / MISS JONES</t>
+  </si>
+  <si>
+    <t>JENKINS / BRATT / MISS JONES / TACKABERRY / EXECUTIVES / FINCH / WOMPER / BUD / PETERSON</t>
+  </si>
+  <si>
+    <t>9A</t>
+  </si>
+  <si>
+    <t>EVERYONE</t>
+  </si>
 </sst>
 </file>
 
@@ -754,7 +903,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\(###\)\ ###\-####"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -833,6 +982,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -860,7 +1017,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1018,6 +1175,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1864,7 +2027,7 @@
         <v>3</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H21" s="25">
         <v>19</v>
@@ -1890,7 +2053,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="H22" s="25">
         <v>20</v>
@@ -1910,7 +2073,7 @@
       <c r="E23" s="22"/>
       <c r="F23" s="9"/>
       <c r="G23" s="10" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H23" s="25">
         <v>21</v>
@@ -1936,7 +2099,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="H24" s="25">
         <v>22</v>
@@ -1962,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H25" s="25">
         <v>23</v>
@@ -2144,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FED2AE-CC40-A149-B7C9-8B9701A2964F}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" style="41" customWidth="1"/>
@@ -2155,37 +2318,39 @@
     <col min="6" max="6" width="26.1640625" style="40" customWidth="1"/>
     <col min="7" max="7" width="23.5" style="41" customWidth="1"/>
     <col min="8" max="8" width="23.5" style="42" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="41"/>
+    <col min="9" max="9" width="28.1640625" style="40" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="31" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="31" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>127</v>
-      </c>
       <c r="H1" s="35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+      <c r="I1" s="34"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
     </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
         <v>103</v>
       </c>
@@ -2196,19 +2361,22 @@
         <v>1</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H3" s="46" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="I3" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
       <c r="B4" s="43">
         <f>B3+1</f>
         <v>2</v>
@@ -2217,37 +2385,43 @@
         <v>2</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.2">
       <c r="B5" s="43">
-        <f t="shared" ref="B5:B19" si="0">B4+1</f>
+        <f t="shared" ref="B5:B24" si="0">B4+1</f>
         <v>3</v>
       </c>
       <c r="C5" s="43">
         <v>13</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="B6" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2259,18 +2433,21 @@
         <v>107</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B7" s="43" t="s">
-        <v>174</v>
+        <v>136</v>
+      </c>
+      <c r="I6" s="40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B7" s="43">
+        <v>4.0999999999999996</v>
       </c>
       <c r="C7" s="43">
         <v>22</v>
@@ -2279,18 +2456,21 @@
         <v>106</v>
       </c>
       <c r="E7" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="B8" s="43" t="s">
-        <v>175</v>
+      <c r="I7" s="40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+      <c r="B8" s="43">
+        <v>4.2</v>
       </c>
       <c r="C8" s="43">
         <v>23</v>
@@ -2299,504 +2479,791 @@
         <v>107</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B9" s="43"/>
+        <v>194</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B9" s="43">
+        <v>4.2</v>
+      </c>
       <c r="C9" s="43">
         <v>33</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>184</v>
-      </c>
-      <c r="H9" s="46"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+      <c r="H9" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B10" s="43">
+        <v>4.2</v>
+      </c>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="45"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="I10" s="40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="43">
         <f>B6+1</f>
         <v>5</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C11" s="43">
         <v>38</v>
       </c>
-      <c r="D10" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B11" s="43">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C11" s="43">
+      <c r="D11" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B12" s="43">
+        <v>6.1</v>
+      </c>
+      <c r="C12" s="43">
         <v>40</v>
       </c>
-      <c r="D11" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="54"/>
-      <c r="H11" s="46" t="s">
+      <c r="D12" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="40" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B12" s="43">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C12" s="43">
+      <c r="G12" s="54"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="40" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="43">
+        <v>6.2</v>
+      </c>
+      <c r="C13" s="43">
+        <v>42</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B14" s="43">
+        <f>B12+1</f>
+        <v>7.1</v>
+      </c>
+      <c r="C14" s="43">
         <v>45</v>
       </c>
-      <c r="D12" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="51" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B13" s="43">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C13" s="43">
+      <c r="D14" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="41"/>
+      <c r="I14" s="40" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B15" s="43">
+        <v>7.2</v>
+      </c>
+      <c r="C15" s="43">
+        <v>49</v>
+      </c>
+      <c r="D15" s="44"/>
+      <c r="E15" s="45"/>
+      <c r="H15" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="I15" s="40" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="43">
+        <v>7.2</v>
+      </c>
+      <c r="C16" s="43">
+        <v>55</v>
+      </c>
+      <c r="D16" s="44"/>
+      <c r="E16" s="45"/>
+      <c r="H16" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B17" s="43">
+        <f>B14+1</f>
+        <v>8.1</v>
+      </c>
+      <c r="C17" s="43">
         <v>56</v>
       </c>
-      <c r="D13" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B14" s="43">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C14" s="43">
-        <v>64</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="56" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="B15" s="43">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C15" s="43">
-        <v>68</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="G15" s="55" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B16" s="43">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C16" s="43">
-        <v>69</v>
-      </c>
-      <c r="D16" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="F16" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="H16" s="46" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B17" s="43">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C17" s="43">
-        <v>72</v>
-      </c>
       <c r="D17" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="I17" s="40" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B18" s="43">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="C18" s="43">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.2">
       <c r="B19" s="43">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="C19" s="43">
+        <v>68</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B20" s="43">
+        <f t="shared" si="0"/>
+        <v>11.1</v>
+      </c>
+      <c r="C20" s="43">
+        <v>69</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="46"/>
+      <c r="I20" s="40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="48"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B22" s="43">
+        <f>B20+1</f>
+        <v>12.1</v>
+      </c>
+      <c r="C22" s="43">
+        <v>72</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="43">
+        <f t="shared" si="0"/>
+        <v>13.1</v>
+      </c>
+      <c r="C23" s="43">
+        <v>76</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B24" s="43">
+        <f t="shared" si="0"/>
+        <v>14.1</v>
+      </c>
+      <c r="C24" s="43">
         <v>79</v>
       </c>
-      <c r="D19" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19" s="38" t="s">
+      <c r="D24" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="41"/>
+      <c r="I24" s="40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B25" s="43">
+        <v>14.2</v>
+      </c>
+      <c r="C25" s="43">
+        <v>81</v>
+      </c>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="38"/>
+      <c r="H25" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="I25" s="40" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="43">
+        <v>14.3</v>
+      </c>
+      <c r="C26" s="43">
+        <v>87</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="38"/>
+      <c r="H26" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="I26" s="40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="43">
+        <v>14.4</v>
+      </c>
+      <c r="C27" s="39">
+        <v>91</v>
+      </c>
+      <c r="D27" s="40"/>
+      <c r="E27" s="43"/>
+      <c r="H27" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="I27" s="40" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="A28" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="43">
+        <v>1</v>
+      </c>
+      <c r="C28" s="43">
+        <v>93</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="51" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="38"/>
-      <c r="H20" s="51"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D21" s="40"/>
-      <c r="E21" s="43"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="43">
-        <v>1</v>
-      </c>
-      <c r="C22" s="43">
-        <v>93</v>
-      </c>
-      <c r="D22" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="40" t="s">
+      <c r="I28" s="40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B29" s="43">
+        <f t="shared" ref="B29:B35" si="1">B28+1</f>
+        <v>2</v>
+      </c>
+      <c r="C29" s="43">
+        <v>99</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="H22" s="52" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B23" s="43">
-        <f t="shared" ref="B23:B30" si="1">B22+1</f>
-        <v>2</v>
-      </c>
-      <c r="C23" s="43">
-        <v>99</v>
-      </c>
-      <c r="D23" s="44" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="46" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B24" s="43">
+      <c r="H29" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="40" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="43">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C30" s="43">
         <v>105</v>
       </c>
-      <c r="D24" s="44" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="H24" s="46" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="47" customFormat="1" ht="28" x14ac:dyDescent="0.2">
-      <c r="B25" s="43">
+      <c r="D30" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="I30" s="40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="B31" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C31" s="43">
         <v>111</v>
       </c>
-      <c r="D25" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="B26" s="43">
+      <c r="D31" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="40"/>
+      <c r="G31" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="B32" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C32" s="43">
         <v>115</v>
       </c>
-      <c r="D26" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="G26" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" s="40"/>
-    </row>
-    <row r="27" spans="1:8" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="B27" s="43">
+      <c r="D32" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="B33" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C33" s="43">
         <v>125</v>
       </c>
-      <c r="D27" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="H27" s="40" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B28" s="43">
+      <c r="D33" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="G33" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="I33" s="40" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B34" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C28" s="43">
+      <c r="C34" s="43">
         <v>128</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D34" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="46" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="43">
+      <c r="I34" s="40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B35" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C35" s="43">
         <v>133</v>
       </c>
-      <c r="D29" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="G29" s="41" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B30" s="43">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="C30" s="43">
+      <c r="D35" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="D30" s="44" t="s">
-        <v>159</v>
-      </c>
-      <c r="E30" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="H30" s="46" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="C31" s="43">
+      <c r="G35" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="40" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B36" s="43">
+        <v>9.1</v>
+      </c>
+      <c r="C36" s="43">
+        <v>134</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="41"/>
+      <c r="I36" s="40" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B37" s="43">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="C37" s="43">
+        <v>139</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="B38" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="43">
         <v>143</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D38" s="44"/>
+      <c r="E38" s="45"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B39" s="43">
+        <f>B36+1</f>
+        <v>10.1</v>
+      </c>
+      <c r="C39" s="43">
+        <v>143</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="H39" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="H31" s="46"/>
-    </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="B32" s="43">
-        <f>B30+1</f>
-        <v>10</v>
-      </c>
-      <c r="C32" s="43">
-        <v>143</v>
-      </c>
-      <c r="D32" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="H32" s="54" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="45"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D34" s="40"/>
-      <c r="E34" s="43"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D35" s="44"/>
-      <c r="E35" s="45"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D36" s="44"/>
-      <c r="E36" s="45"/>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D37" s="44"/>
-      <c r="E37" s="45"/>
+      <c r="I39" s="40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="45"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="D41" s="40"/>
+      <c r="E41" s="43"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="D42" s="44"/>
+      <c r="E42" s="45"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="D43" s="44"/>
+      <c r="E43" s="45"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="D44" s="44"/>
+      <c r="E44" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E37B0F-1285-D242-A866-6ABEE0A812B7}">
+  <dimension ref="A2:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="26"/>
+    <col min="2" max="2" width="10.83203125" style="27"/>
+    <col min="3" max="3" width="92.5" style="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="195" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="27">
+        <v>1</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="27">
+        <v>2</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="77" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="27">
+        <v>3</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="27">
+        <v>5</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="27">
+        <v>9</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="27">
+        <v>2</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B11" s="27">
+        <v>5</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="B12" s="27">
+        <v>7</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/howTo26/How2$ production.xlsx
+++ b/howTo26/How2$ production.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92565AEA-86EB-F84C-B745-33A025BC2965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAA4280-96CB-5546-99D5-FC3FB093751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1000" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="246">
   <si>
     <t xml:space="preserve">EMERGENCY CONTACT </t>
   </si>
@@ -391,34 +391,18 @@
     <t>Down Stage Right</t>
   </si>
   <si>
-    <t>fencing and plants</t>
-  </si>
-  <si>
     <t xml:space="preserve">clear terrance </t>
   </si>
   <si>
-    <t>need couch down stage left
-skip half-wall</t>
-  </si>
-  <si>
-    <t>Back to both executive office</t>
-  </si>
-  <si>
     <t>Cinderella Darling</t>
   </si>
   <si>
     <t>Executive Office stage left</t>
   </si>
   <si>
-    <t>larger table with 7 to 8 chairs, chart easel</t>
-  </si>
-  <si>
     <t>Pirate Dance</t>
   </si>
   <si>
-    <t>chairs toppled over maybe a desk, typewriter, waste basket</t>
-  </si>
-  <si>
     <t>no change</t>
   </si>
   <si>
@@ -467,16 +451,7 @@
     <t>Closes</t>
   </si>
   <si>
-    <t>Bring in mailroom wall</t>
-  </si>
-  <si>
-    <t>need intercom</t>
-  </si>
-  <si>
     <t>see above</t>
-  </si>
-  <si>
-    <t>starts middle of pg. 23</t>
   </si>
   <si>
     <t>pg. 22 Bigley is the executive office on stage right</t>
@@ -504,10 +479,6 @@
 - Grand Old Ivy (Reprise)</t>
   </si>
   <si>
-    <t>- desk and chair for Gatch and door
-- chair &amp; desk for Miss Krumholtz</t>
-  </si>
-  <si>
     <t>Building corridor </t>
   </si>
   <si>
@@ -553,9 +524,6 @@
     <t xml:space="preserve">Stage right </t>
   </si>
   <si>
-    <t>Stage left</t>
-  </si>
-  <si>
     <t>sinks come on</t>
   </si>
   <si>
@@ -569,29 +537,6 @@
   </si>
   <si>
     <t>Office is stage right in front of Biggley's office.  Desk &amp; chair</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Traveler opens</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> but no desks  or some in front of the half-wall</t>
-    </r>
   </si>
   <si>
     <r>
@@ -651,9 +596,6 @@
     <t>Plans &amp; Systems Office</t>
   </si>
   <si>
-    <t>- desk and chair</t>
-  </si>
-  <si>
     <t>- strike mailroom stage left
 - strike outer office stage right</t>
   </si>
@@ -669,9 +611,6 @@
   <si>
     <t>Moving wall oppossite mailroom wall.
 Some guys are watching in the boardroom or not. May need an old TV.</t>
-  </si>
-  <si>
-    <t>Scrubwomen 'cleaning up'</t>
   </si>
   <si>
     <t>Book Voice Scenes</t>
@@ -894,6 +833,98 @@
   </si>
   <si>
     <t>EVERYONE</t>
+  </si>
+  <si>
+    <t>Characters</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>The same 4 desks as in scene 2</t>
+  </si>
+  <si>
+    <t>4 secretay desks</t>
+  </si>
+  <si>
+    <t>chairs toppled over maybe a desk, typewriter, waste basket
+Scrubwomen 'cleaning up'</t>
+  </si>
+  <si>
+    <t>Door and down stage left</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Traveler opens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> just 4 secretary desks</t>
+    </r>
+  </si>
+  <si>
+    <t>Bring in mailroom wall; phone table on wall by the stairs stage left; table in centered of wall with wall being 3/4 feet from stage left
+Biggley table stage right</t>
+  </si>
+  <si>
+    <t>just Biggley desk and chair; need intercom</t>
+  </si>
+  <si>
+    <t>starts middle of pg. 23
+stage crew takes off Biggley desk when Twimble/Finch enter</t>
+  </si>
+  <si>
+    <t>use the other real desk</t>
+  </si>
+  <si>
+    <t>use the other real desk; down stage right</t>
+  </si>
+  <si>
+    <t>just Biggley desk and chair</t>
+  </si>
+  <si>
+    <t>same as 4.1</t>
+  </si>
+  <si>
+    <t>Same as 2/3</t>
+  </si>
+  <si>
+    <t>- desk and chair; pony wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- use other real desk and chair for Gatch </t>
+  </si>
+  <si>
+    <t>bar cart, fencing and plants</t>
+  </si>
+  <si>
+    <t>need couch down stage left, Biggley desk and chair stage right, door, and pony wall</t>
+  </si>
+  <si>
+    <t>no couch</t>
+  </si>
+  <si>
+    <t>larger table with 8 chairs</t>
+  </si>
+  <si>
+    <t>TV show is Stage left; business men are stage right - need 4 chairs and TV</t>
+  </si>
+  <si>
+    <t>using 4 secretary desks, 4 chairs</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1048,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1113,9 +1144,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1144,9 +1172,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1159,10 +1184,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1181,6 +1202,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2027,7 +2051,7 @@
         <v>3</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="H21" s="25">
         <v>19</v>
@@ -2053,7 +2077,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H22" s="25">
         <v>20</v>
@@ -2073,7 +2097,7 @@
       <c r="E23" s="22"/>
       <c r="F23" s="9"/>
       <c r="G23" s="10" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="H23" s="25">
         <v>21</v>
@@ -2099,7 +2123,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H24" s="25">
         <v>22</v>
@@ -2125,7 +2149,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="H25" s="25">
         <v>23</v>
@@ -2155,7 +2179,7 @@
       <c r="A28" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="53" t="s">
         <v>81</v>
       </c>
       <c r="C28" s="18">
@@ -2310,862 +2334,879 @@
   <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.5" style="41" customWidth="1"/>
-    <col min="2" max="2" width="5" style="41" customWidth="1"/>
-    <col min="3" max="3" width="4.83203125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="7.5" style="39" customWidth="1"/>
-    <col min="6" max="6" width="26.1640625" style="40" customWidth="1"/>
-    <col min="7" max="7" width="23.5" style="41" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="42" customWidth="1"/>
-    <col min="9" max="9" width="28.1640625" style="40" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="41"/>
+    <col min="1" max="1" width="4.5" style="40" customWidth="1"/>
+    <col min="2" max="2" width="5" style="40" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" style="40" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="37" customWidth="1"/>
+    <col min="5" max="5" width="7.5" style="38" customWidth="1"/>
+    <col min="6" max="6" width="26.1640625" style="39" customWidth="1"/>
+    <col min="7" max="7" width="23.5" style="40" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="39" customWidth="1"/>
+    <col min="9" max="9" width="28.1640625" style="39" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="31" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="33" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D1" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="42">
+        <v>1</v>
+      </c>
+      <c r="C3" s="42">
+        <v>1</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="H1" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-    </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="43">
-        <v>1</v>
-      </c>
-      <c r="C3" s="43">
-        <v>1</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="39" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="B4" s="43">
+    <row r="4" spans="1:9" s="45" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="B4" s="42">
         <f>B3+1</f>
         <v>2</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="42">
         <v>2</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="H4" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>191</v>
+      <c r="F4" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="B5" s="43">
+      <c r="B5" s="42">
         <f t="shared" ref="B5:B24" si="0">B4+1</f>
         <v>3</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="42">
         <v>13</v>
       </c>
-      <c r="D5" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B6" s="43">
+      <c r="D5" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+      <c r="B6" s="42">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="42">
         <v>22</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="42" t="s">
+      <c r="E6" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="40" t="s">
-        <v>192</v>
+      <c r="G6" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B7" s="43">
+      <c r="B7" s="42">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="42">
         <v>22</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>193</v>
+      <c r="E7" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="B8" s="43">
+      <c r="B8" s="42">
         <v>4.2</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="42">
         <v>23</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="I8" s="40" t="s">
-        <v>195</v>
+      <c r="E8" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="B9" s="43">
+      <c r="B9" s="42">
         <v>4.2</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="42">
         <v>33</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>198</v>
+      <c r="F9" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B10" s="43">
+      <c r="B10" s="42">
         <v>4.2</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="45"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="I10" s="40" t="s">
-        <v>199</v>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B11" s="43">
+      <c r="B11" s="42">
         <f>B6+1</f>
         <v>5</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="42">
         <v>38</v>
       </c>
-      <c r="D11" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="45" t="s">
+      <c r="D11" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B12" s="42">
+        <v>6.1</v>
+      </c>
+      <c r="C12" s="42">
+        <v>40</v>
+      </c>
+      <c r="D12" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="I11" s="40" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B12" s="43">
-        <v>6.1</v>
-      </c>
-      <c r="C12" s="43">
-        <v>40</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="40" t="s">
-        <v>201</v>
+      <c r="E12" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="49"/>
+      <c r="I12" s="39" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B13" s="43">
+      <c r="B13" s="42">
         <v>6.2</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="42">
         <v>42</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="45"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>202</v>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="B14" s="43">
+      <c r="B14" s="42">
         <f>B12+1</f>
         <v>7.1</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="42">
         <v>45</v>
       </c>
-      <c r="D14" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="40" t="s">
+      <c r="D14" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="41"/>
-      <c r="I14" s="40" t="s">
-        <v>203</v>
+      <c r="H14" s="45"/>
+      <c r="I14" s="39" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B15" s="43">
+      <c r="B15" s="42">
         <v>7.2</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="42">
         <v>49</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="45"/>
-      <c r="H15" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="I15" s="40" t="s">
-        <v>206</v>
+      <c r="D15" s="43"/>
+      <c r="E15" s="44"/>
+      <c r="H15" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B16" s="43">
+      <c r="B16" s="42">
         <v>7.2</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="42">
         <v>55</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
-      <c r="H16" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>207</v>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44"/>
+      <c r="H16" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B17" s="43">
+      <c r="B17" s="42">
         <f>B14+1</f>
         <v>8.1</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="42">
         <v>56</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="40" t="s">
-        <v>208</v>
+      <c r="F17" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B18" s="43">
+      <c r="B18" s="42">
         <f t="shared" si="0"/>
         <v>9.1</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="42">
         <v>64</v>
       </c>
-      <c r="D18" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="40" t="s">
+      <c r="D18" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="56" t="s">
-        <v>174</v>
-      </c>
-      <c r="I18" s="40" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="B19" s="43">
+      <c r="G18" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="B19" s="42">
         <f t="shared" si="0"/>
         <v>10.1</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="42">
         <v>68</v>
       </c>
-      <c r="D19" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="E19" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F19" s="40" t="s">
+      <c r="D19" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>210</v>
+      <c r="G19" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B20" s="43">
+      <c r="B20" s="42">
         <f t="shared" si="0"/>
         <v>11.1</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="42">
         <v>69</v>
       </c>
-      <c r="D20" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="40" t="s">
+      <c r="D20" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="40" t="s">
-        <v>211</v>
+      <c r="G20" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" s="49"/>
+      <c r="I20" s="39" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="48"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>213</v>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="46"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="B22" s="43">
+      <c r="B22" s="42">
         <f>B20+1</f>
         <v>12.1</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="42">
         <v>72</v>
       </c>
-      <c r="D22" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="54" t="s">
-        <v>214</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>215</v>
+      <c r="D22" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="H22" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="I22" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B23" s="43">
+      <c r="B23" s="42">
         <f t="shared" si="0"/>
         <v>13.1</v>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="42">
         <v>76</v>
       </c>
-      <c r="D23" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B24" s="43">
+      <c r="D23" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B24" s="42">
         <f t="shared" si="0"/>
         <v>14.1</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="42">
         <v>79</v>
       </c>
-      <c r="D24" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="H24" s="41"/>
-      <c r="I24" s="40" t="s">
-        <v>217</v>
+      <c r="D24" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="H24" s="45"/>
+      <c r="I24" s="39" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B25" s="43">
+      <c r="B25" s="42">
         <v>14.2</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="42">
         <v>81</v>
       </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="38"/>
-      <c r="H25" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" s="40" t="s">
-        <v>218</v>
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="37"/>
+      <c r="H25" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B26" s="43">
+      <c r="B26" s="42">
         <v>14.3</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="42">
         <v>87</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="38"/>
-      <c r="H26" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="I26" s="40" t="s">
-        <v>220</v>
+      <c r="D26" s="43"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="37"/>
+      <c r="H26" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="I26" s="39" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B27" s="43">
+      <c r="B27" s="42">
         <v>14.4</v>
       </c>
-      <c r="C27" s="39">
+      <c r="C27" s="38">
         <v>91</v>
       </c>
-      <c r="D27" s="40"/>
-      <c r="E27" s="43"/>
-      <c r="H27" s="54" t="s">
-        <v>222</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>223</v>
+      <c r="D27" s="39"/>
+      <c r="E27" s="42"/>
+      <c r="H27" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="A28" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="43">
+      <c r="A28" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="42">
         <v>1</v>
       </c>
-      <c r="C28" s="43">
+      <c r="C28" s="42">
         <v>93</v>
       </c>
-      <c r="D28" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="H28" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="I28" s="40" t="s">
-        <v>224</v>
+      <c r="D28" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="H28" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" s="39" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B29" s="43">
+      <c r="B29" s="42">
         <f t="shared" ref="B29:B35" si="1">B28+1</f>
         <v>2</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="42">
         <v>99</v>
       </c>
-      <c r="D29" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F29" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="H29" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29" s="40" t="s">
-        <v>225</v>
+      <c r="D29" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="H29" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B30" s="43">
+      <c r="B30" s="42">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="42">
         <v>105</v>
       </c>
-      <c r="D30" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="H30" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="I30" s="40" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="B31" s="43">
+      <c r="D30" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" s="39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="B31" s="42">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C31" s="43">
+      <c r="C31" s="42">
         <v>111</v>
       </c>
-      <c r="D31" s="44" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="H31" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="I31" s="40" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="B32" s="43">
+      <c r="D31" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="B32" s="42">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C32" s="43">
+      <c r="C32" s="42">
         <v>115</v>
       </c>
-      <c r="D32" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G32" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="B33" s="43">
+      <c r="D32" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>243</v>
+      </c>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="45" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="B33" s="42">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="42">
         <v>125</v>
       </c>
-      <c r="D33" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="E33" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="I33" s="40" t="s">
-        <v>229</v>
+      <c r="D33" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="39" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="B34" s="43">
+      <c r="B34" s="42">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="42">
         <v>128</v>
       </c>
-      <c r="D34" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="G34" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="I34" s="40" t="s">
-        <v>230</v>
+      <c r="D34" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="G34" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B35" s="43">
+      <c r="B35" s="42">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C35" s="43">
+      <c r="C35" s="42">
         <v>133</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="43"/>
+      <c r="E35" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="B36" s="42">
+        <v>9.1</v>
+      </c>
+      <c r="C36" s="42">
+        <v>134</v>
+      </c>
+      <c r="D36" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="G35" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="I35" s="40" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="B36" s="43">
-        <v>9.1</v>
-      </c>
-      <c r="C36" s="43">
-        <v>134</v>
-      </c>
-      <c r="D36" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="H36" s="41"/>
-      <c r="I36" s="40" t="s">
-        <v>233</v>
+      <c r="E36" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="H36" s="45"/>
+      <c r="I36" s="39" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B37" s="43">
+      <c r="B37" s="42">
         <v>9.1999999999999993</v>
       </c>
-      <c r="C37" s="43">
+      <c r="C37" s="42">
         <v>139</v>
       </c>
-      <c r="D37" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="H37" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="I37" s="40" t="s">
-        <v>232</v>
+      <c r="D37" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="I37" s="39" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="B38" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="43">
+      <c r="B38" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="C38" s="42">
         <v>143</v>
       </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="45"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="40" t="s">
-        <v>235</v>
+      <c r="D38" s="43"/>
+      <c r="E38" s="44"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="39" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="B39" s="43">
+      <c r="B39" s="42">
         <f>B36+1</f>
         <v>10.1</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="42">
         <v>143</v>
       </c>
-      <c r="D39" s="44" t="s">
+      <c r="D39" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="E39" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F39" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="H39" s="54" t="s">
-        <v>172</v>
-      </c>
-      <c r="I39" s="40" t="s">
-        <v>235</v>
+      <c r="F39" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" s="39" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="45"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="44"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="D41" s="40"/>
-      <c r="E41" s="43"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="42"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="D42" s="44"/>
-      <c r="E42" s="45"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="44"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="D43" s="44"/>
-      <c r="E43" s="45"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="44"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="D44" s="44"/>
-      <c r="E44" s="45"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3184,13 +3225,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="59" t="s">
-        <v>181</v>
+      <c r="A2" s="55" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" s="27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="195" customHeight="1" x14ac:dyDescent="0.2">
@@ -3200,67 +3241,67 @@
       <c r="B5" s="27">
         <v>1</v>
       </c>
-      <c r="C5" s="58" t="s">
-        <v>182</v>
+      <c r="C5" s="54" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="27">
         <v>2</v>
       </c>
-      <c r="C6" s="58" t="s">
-        <v>183</v>
+      <c r="C6" s="54" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="77" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="27">
         <v>3</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>184</v>
+      <c r="C7" s="54" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="27">
         <v>5</v>
       </c>
-      <c r="C8" s="58" t="s">
-        <v>185</v>
+      <c r="C8" s="54" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="27">
         <v>9</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>186</v>
+      <c r="C9" s="54" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B10" s="27">
         <v>2</v>
       </c>
-      <c r="C10" s="58" t="s">
-        <v>187</v>
+      <c r="C10" s="54" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="27">
         <v>5</v>
       </c>
-      <c r="C11" s="58" t="s">
-        <v>188</v>
+      <c r="C11" s="54" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="B12" s="27">
         <v>7</v>
       </c>
-      <c r="C12" s="58" t="s">
-        <v>189</v>
+      <c r="C12" s="54" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/howTo26/How2$ production.xlsx
+++ b/howTo26/How2$ production.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAA4280-96CB-5546-99D5-FC3FB093751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1623C1-D135-8449-9926-C7FB9904348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="600" windowWidth="27860" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
+    <workbookView xWindow="-26280" yWindow="760" windowWidth="21220" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
-    <sheet name="Scenes" sheetId="2" r:id="rId2"/>
-    <sheet name="Book Voice" sheetId="3" r:id="rId3"/>
+    <sheet name="Props" sheetId="5" r:id="rId2"/>
+    <sheet name="Scenes" sheetId="2" r:id="rId3"/>
+    <sheet name="Book Voice" sheetId="3" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="364">
   <si>
     <t xml:space="preserve">EMERGENCY CONTACT </t>
   </si>
@@ -434,9 +438,6 @@
   </si>
   <si>
     <t>Traveler</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> with scaffolding</t>
   </si>
   <si>
     <t>closed</t>
@@ -926,6 +927,363 @@
   <si>
     <t>using 4 secretary desks, 4 chairs</t>
   </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>ACT I</t>
+  </si>
+  <si>
+    <t>Scene 1</t>
+  </si>
+  <si>
+    <t>Scene 2</t>
+  </si>
+  <si>
+    <t>Tackaberry</t>
+  </si>
+  <si>
+    <t>Office Boy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosemary </t>
+  </si>
+  <si>
+    <t>Scene 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensemble </t>
+  </si>
+  <si>
+    <t>Office Employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Girl in Ensemble </t>
+  </si>
+  <si>
+    <t>SCENE 4</t>
+  </si>
+  <si>
+    <t>Biggley</t>
+  </si>
+  <si>
+    <t>Twimble</t>
+  </si>
+  <si>
+    <t>Scene 7</t>
+  </si>
+  <si>
+    <t>Scene 8</t>
+  </si>
+  <si>
+    <t>Scrub women</t>
+  </si>
+  <si>
+    <t>SCENE 9</t>
+  </si>
+  <si>
+    <t>SCENE 10</t>
+  </si>
+  <si>
+    <t>Miss Kromholtz</t>
+  </si>
+  <si>
+    <t>SCENE 11</t>
+  </si>
+  <si>
+    <t>SCENE 12</t>
+  </si>
+  <si>
+    <t>Ensemble</t>
+  </si>
+  <si>
+    <t>Waiters</t>
+  </si>
+  <si>
+    <t>SCENE 14</t>
+  </si>
+  <si>
+    <t>ACT II</t>
+  </si>
+  <si>
+    <t>SCENE 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Girls </t>
+  </si>
+  <si>
+    <t>SCENE 2</t>
+  </si>
+  <si>
+    <t>SCENE 3</t>
+  </si>
+  <si>
+    <t>SCENE 5</t>
+  </si>
+  <si>
+    <t>Office Boys</t>
+  </si>
+  <si>
+    <t>Men</t>
+  </si>
+  <si>
+    <t>SCENE 6</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>SCENE 7</t>
+  </si>
+  <si>
+    <t>Disastrous office space; equipment everywhere, debris, etc</t>
+  </si>
+  <si>
+    <t>SCENE 8</t>
+  </si>
+  <si>
+    <t>Girls</t>
+  </si>
+  <si>
+    <t>FINAL SCENE</t>
+  </si>
+  <si>
+    <t>WINDOW WIPER, Bucket</t>
+  </si>
+  <si>
+    <t>BOOK TITLED “HOW TO SUCCEED IN BUSINESS WITHOUT REALLY TRYING”.</t>
+  </si>
+  <si>
+    <t>CLIPBOARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notebook </t>
+  </si>
+  <si>
+    <t>CIGAR</t>
+  </si>
+  <si>
+    <t>Matches</t>
+  </si>
+  <si>
+    <t>Mail basket</t>
+  </si>
+  <si>
+    <t>Folder of papers</t>
+  </si>
+  <si>
+    <t>Covers</t>
+  </si>
+  <si>
+    <t>Period appropriate office equipment</t>
+  </si>
+  <si>
+    <t>Desks</t>
+  </si>
+  <si>
+    <t>Typewriters</t>
+  </si>
+  <si>
+    <t>Period appropriate office machinery</t>
+  </si>
+  <si>
+    <t>Coffee mugs or cups</t>
+  </si>
+  <si>
+    <t>Coffee machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coffee Pot </t>
+  </si>
+  <si>
+    <t>Basket of mail</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>Papers on desk</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Intercom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desk with drawer </t>
+  </si>
+  <si>
+    <t>Knitting supplies and yarn</t>
+  </si>
+  <si>
+    <t>Mail bag</t>
+  </si>
+  <si>
+    <t>Medal</t>
+  </si>
+  <si>
+    <t>Lapel</t>
+  </si>
+  <si>
+    <t>Newspaper</t>
+  </si>
+  <si>
+    <t>Mops</t>
+  </si>
+  <si>
+    <t>Cleaning supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cigarettes </t>
+  </si>
+  <si>
+    <t>Covered typewriters</t>
+  </si>
+  <si>
+    <t>Attache’ case</t>
+  </si>
+  <si>
+    <t>Papers</t>
+  </si>
+  <si>
+    <t>Paper coffee cups</t>
+  </si>
+  <si>
+    <t>Ashtray</t>
+  </si>
+  <si>
+    <t>Cigarette butts</t>
+  </si>
+  <si>
+    <t>Machine tape</t>
+  </si>
+  <si>
+    <t>Lamp</t>
+  </si>
+  <si>
+    <t>Knitting supplies/yarn</t>
+  </si>
+  <si>
+    <t>Clubs</t>
+  </si>
+  <si>
+    <t>Steno pad</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>Folder</t>
+  </si>
+  <si>
+    <t>Dress Box</t>
+  </si>
+  <si>
+    <t>Martini, champagne, cocktail glasses</t>
+  </si>
+  <si>
+    <t>Rolling bar</t>
+  </si>
+  <si>
+    <t>Martini glass with olive</t>
+  </si>
+  <si>
+    <t>Towel</t>
+  </si>
+  <si>
+    <t>Lipstick smeared on face</t>
+  </si>
+  <si>
+    <t>Phone on desk</t>
+  </si>
+  <si>
+    <t>Pen and resignation form</t>
+  </si>
+  <si>
+    <t>Hat, bag, coat</t>
+  </si>
+  <si>
+    <t>Waste basket</t>
+  </si>
+  <si>
+    <t>Tissues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper folded into flower bouquet </t>
+  </si>
+  <si>
+    <t>Script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letter </t>
+  </si>
+  <si>
+    <t>Knitting supplies</t>
+  </si>
+  <si>
+    <t>Handkerchief</t>
+  </si>
+  <si>
+    <t>Electric razor?</t>
+  </si>
+  <si>
+    <t>Cone-shaped chairs</t>
+  </si>
+  <si>
+    <t>Backdrop with various charts and maps</t>
+  </si>
+  <si>
+    <t>Painting of Mt Vesuvius</t>
+  </si>
+  <si>
+    <t>Cover Of Newsweek Biggleys Picture</t>
+  </si>
+  <si>
+    <t>Cover Of Sports Illustrated Biggley’s Picture</t>
+  </si>
+  <si>
+    <t>Photo Of Finch titled “The End”</t>
+  </si>
+  <si>
+    <t>Folder with papers</t>
+  </si>
+  <si>
+    <t>Easel titled “A Finch Presentation”</t>
+  </si>
+  <si>
+    <t>Cricket</t>
+  </si>
+  <si>
+    <t>Toy rocket</t>
+  </si>
+  <si>
+    <t>Large map</t>
+  </si>
+  <si>
+    <t>Flips card with sales chart in red, trending down</t>
+  </si>
+  <si>
+    <t>Microphone</t>
+  </si>
+  <si>
+    <t>TV Logo that looks like globe</t>
+  </si>
+  <si>
+    <t>Cutout Pirate ship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large Treasure Chest </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large Bible </t>
+  </si>
+  <si>
+    <t>Handkerchiefs</t>
+  </si>
+  <si>
+    <t>How to succeed… Book</t>
+  </si>
 </sst>
 </file>
 
@@ -934,7 +1292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\(###\)\ ###\-####"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1021,6 +1379,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1048,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1205,6 +1599,36 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1221,6 +1645,40 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cast"/>
+      <sheetName val="Props"/>
+      <sheetName val="Scenes"/>
+      <sheetName val="Book Voice"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="35">
+          <cell r="C35" t="str">
+            <v xml:space="preserve">Desk with drawer </v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36" t="str">
+            <v>Knitting supplies and yarn</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2051,7 +2509,7 @@
         <v>3</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H21" s="25">
         <v>19</v>
@@ -2077,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H22" s="25">
         <v>20</v>
@@ -2097,7 +2555,7 @@
       <c r="E23" s="22"/>
       <c r="F23" s="9"/>
       <c r="G23" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H23" s="25">
         <v>21</v>
@@ -2123,7 +2581,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H24" s="25">
         <v>22</v>
@@ -2149,7 +2607,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H25" s="25">
         <v>23</v>
@@ -2330,6 +2788,750 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECC77CA-906B-0942-857F-DDC2F9F31BBF}">
+  <dimension ref="A3:C132"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="63" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="61"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="61" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="C7" s="65" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="60"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="61" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B14" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" s="62" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="60"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="61" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="62" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="64" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C20" s="64" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C21" s="64" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C22" s="64" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C23" s="64" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C24" s="64" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="60"/>
+      <c r="B25" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="C25" s="64" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B26" s="60" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B28" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="64" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C29" s="64" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="60"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="61" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="64" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C34" s="64" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C35" s="66" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="60"/>
+      <c r="C36" s="66" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="64" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B39" s="60"/>
+      <c r="C39" s="64" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="61" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="61" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="60"/>
+      <c r="B44" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="C44" s="64" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C45" s="64" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C46" s="64" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B47" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="64" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C48" s="64" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="60"/>
+      <c r="C49" s="64" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C50" s="64" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C51" s="64" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C52" s="64" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C53" s="64" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C54" s="64" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C55" s="66" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C56" s="66" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="61" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="64" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="66" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C60" s="64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="61" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="C62" s="64" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" s="64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="61" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="61" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" s="64" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="60" t="s">
+        <v>268</v>
+      </c>
+      <c r="C68" s="64" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="64" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="61" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="66" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B72" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" s="66" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C73" s="64" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C74" s="64" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="60"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="59" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="61"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="61" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="66" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="C80" s="64" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="60"/>
+      <c r="C81" s="64" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C82" s="64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="61" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C84" s="64" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B85" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" s="64" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B86" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="64" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="61" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B88" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C88" s="64" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B89" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="64" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="61" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B91" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="64" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B92" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C92" s="64" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="61" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C94" s="66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C95" s="64" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C96" s="64" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C97" s="64" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C98" s="64" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C99" s="64" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B100" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" s="64" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C101" s="64" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B102" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="C102" s="64" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C103" s="64" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B104" s="60" t="s">
+        <v>277</v>
+      </c>
+      <c r="C104" s="64" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C105" s="64" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C106" s="64" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="61" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="61"/>
+      <c r="C108" s="64" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C109" s="64" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C110" s="64" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C111" s="64" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="60"/>
+      <c r="B112" s="60" t="s">
+        <v>279</v>
+      </c>
+      <c r="C112" s="64" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="61" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B114" s="60" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="61" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="60" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C117" s="66" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="61" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B119" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C119" s="64" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="61" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="60"/>
+      <c r="B121" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C121" s="64" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="60"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A129" s="60"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A130" s="60"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A131" s="60"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A132" s="60"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FED2AE-CC40-A149-B7C9-8B9701A2964F}">
   <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
@@ -2351,7 +3553,7 @@
         <v>118</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>121</v>
@@ -2369,7 +3571,7 @@
         <v>117</v>
       </c>
       <c r="I1" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -2390,9 +3592,9 @@
         <v>122</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="44" t="s">
         <v>126</v>
       </c>
       <c r="H3" s="49" t="s">
@@ -2414,16 +3616,16 @@
         <v>123</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.2">
@@ -2438,13 +3640,13 @@
         <v>124</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>116</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.2">
@@ -2459,16 +3661,16 @@
         <v>107</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2482,16 +3684,16 @@
         <v>106</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.2">
@@ -2505,19 +3707,19 @@
         <v>107</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>181</v>
-      </c>
-      <c r="I8" s="39" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.2">
@@ -2531,19 +3733,19 @@
         <v>124</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2555,10 +3757,10 @@
       <c r="E10" s="44"/>
       <c r="G10" s="50"/>
       <c r="H10" s="47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2570,19 +3772,19 @@
         <v>38</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2593,20 +3795,20 @@
         <v>40</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G12" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H12" s="49"/>
       <c r="I12" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2620,10 +3822,10 @@
       <c r="E13" s="44"/>
       <c r="G13" s="50"/>
       <c r="H13" s="47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.2">
@@ -2635,17 +3837,17 @@
         <v>45</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F14" s="39" t="s">
         <v>108</v>
       </c>
       <c r="H14" s="45"/>
       <c r="I14" s="39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2658,10 +3860,10 @@
       <c r="D15" s="43"/>
       <c r="E15" s="44"/>
       <c r="H15" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2674,10 +3876,10 @@
       <c r="D16" s="43"/>
       <c r="E16" s="44"/>
       <c r="H16" s="47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2692,16 +3894,16 @@
         <v>124</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H17" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2713,19 +3915,19 @@
         <v>64</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F18" s="39" t="s">
         <v>109</v>
       </c>
       <c r="G18" s="52" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2737,19 +3939,19 @@
         <v>68</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F19" s="39" t="s">
         <v>110</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2761,20 +3963,20 @@
         <v>69</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F20" s="39" t="s">
         <v>104</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H20" s="49"/>
       <c r="I20" s="39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2784,10 +3986,10 @@
       <c r="E21" s="46"/>
       <c r="G21" s="37"/>
       <c r="H21" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" s="39" t="s">
         <v>199</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.2">
@@ -2799,19 +4001,19 @@
         <v>72</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H22" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="I22" s="39" t="s">
         <v>201</v>
-      </c>
-      <c r="I22" s="39" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2823,16 +4025,16 @@
         <v>76</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G23" s="40" t="s">
         <v>111</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.2">
@@ -2844,17 +4046,17 @@
         <v>79</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H24" s="45"/>
       <c r="I24" s="39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2868,10 +4070,10 @@
       <c r="E25" s="44"/>
       <c r="F25" s="37"/>
       <c r="H25" s="47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2885,10 +4087,10 @@
       <c r="E26" s="44"/>
       <c r="F26" s="37"/>
       <c r="H26" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I26" s="39" t="s">
         <v>206</v>
-      </c>
-      <c r="I26" s="39" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2901,15 +4103,15 @@
       <c r="D27" s="39"/>
       <c r="E27" s="42"/>
       <c r="H27" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="I27" s="39" t="s">
         <v>209</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B28" s="42">
         <v>1</v>
@@ -2921,16 +4123,16 @@
         <v>124</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H28" s="56" t="s">
         <v>112</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.2">
@@ -2942,22 +4144,22 @@
         <v>99</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F29" s="39" t="s">
         <v>113</v>
       </c>
       <c r="G29" s="45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I29" s="39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -2969,19 +4171,19 @@
         <v>105</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30" s="40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H30" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I30" s="39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -2993,20 +4195,20 @@
         <v>111</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F31" s="39"/>
       <c r="G31" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H31" s="49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I31" s="39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.2">
@@ -3018,20 +4220,20 @@
         <v>115</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H32" s="39"/>
       <c r="I32" s="39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="2:9" s="45" customFormat="1" ht="75" x14ac:dyDescent="0.2">
@@ -3043,22 +4245,22 @@
         <v>125</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F33" s="39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H33" s="39" t="s">
         <v>114</v>
       </c>
       <c r="I33" s="39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="45" x14ac:dyDescent="0.2">
@@ -3070,22 +4272,22 @@
         <v>128</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G34" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H34" s="49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I34" s="39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.2">
@@ -3098,13 +4300,13 @@
       </c>
       <c r="D35" s="43"/>
       <c r="E35" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I35" s="39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="45" x14ac:dyDescent="0.2">
@@ -3115,17 +4317,17 @@
         <v>134</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F36" s="39" t="s">
         <v>115</v>
       </c>
       <c r="H36" s="45"/>
       <c r="I36" s="39" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="30" x14ac:dyDescent="0.2">
@@ -3136,21 +4338,21 @@
         <v>139</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I37" s="39" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B38" s="42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C38" s="42">
         <v>143</v>
@@ -3159,7 +4361,7 @@
       <c r="E38" s="44"/>
       <c r="H38" s="49"/>
       <c r="I38" s="39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="30" x14ac:dyDescent="0.2">
@@ -3174,16 +4376,16 @@
         <v>124</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F39" s="39" t="s">
         <v>115</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I39" s="39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
@@ -3214,94 +4416,135 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E37B0F-1285-D242-A866-6ABEE0A812B7}">
-  <dimension ref="A2:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="26"/>
-    <col min="2" max="2" width="10.83203125" style="27"/>
-    <col min="3" max="3" width="92.5" style="26" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="61.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C1" s="27"/>
+      <c r="D1" s="26"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C3" s="27"/>
+      <c r="D3" s="26"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="57" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="195" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="195" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
         <v>103</v>
       </c>
       <c r="B5" s="27">
         <v>1</v>
       </c>
-      <c r="C5" s="54" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="27">
+        <v>1</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="27">
         <v>2</v>
       </c>
-      <c r="C6" s="54" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="77" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="27">
+        <v>2</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="77" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="27">
         <v>3</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="27">
+        <v>16</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="27">
+        <v>4</v>
+      </c>
+      <c r="C8" s="27">
+        <v>38</v>
+      </c>
+      <c r="D8" s="54" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="27">
-        <v>5</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="163" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="27">
         <v>9</v>
       </c>
-      <c r="C9" s="54" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="C9" s="27">
+        <v>66</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" s="27">
         <v>2</v>
       </c>
-      <c r="C10" s="54" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="C10" s="27">
+        <v>99</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="187" x14ac:dyDescent="0.2">
       <c r="B11" s="27">
         <v>5</v>
       </c>
-      <c r="C11" s="54" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="C11" s="27">
+        <v>115</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="B12" s="27">
         <v>7</v>
       </c>
-      <c r="C12" s="54" t="s">
-        <v>176</v>
+      <c r="C12" s="27">
+        <v>128</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/howTo26/How2$ production.xlsx
+++ b/howTo26/How2$ production.xlsx
@@ -1,26 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1623C1-D135-8449-9926-C7FB9904348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012C2330-2083-1845-A900-BD12F15F9B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26280" yWindow="760" windowWidth="21220" windowHeight="20600" activeTab="1" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
+    <workbookView xWindow="-26280" yWindow="760" windowWidth="21220" windowHeight="20600" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
     <sheet name="Props" sheetId="5" r:id="rId2"/>
     <sheet name="Scenes" sheetId="2" r:id="rId3"/>
     <sheet name="Book Voice" sheetId="3" r:id="rId4"/>
+    <sheet name="Scenes playbill" sheetId="6" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="364">
   <si>
     <t xml:space="preserve">EMERGENCY CONTACT </t>
   </si>
@@ -1645,40 +1643,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cast"/>
-      <sheetName val="Props"/>
-      <sheetName val="Scenes"/>
-      <sheetName val="Book Voice"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="35">
-          <cell r="C35" t="str">
-            <v xml:space="preserve">Desk with drawer </v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36" t="str">
-            <v>Knitting supplies and yarn</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4511,7 +4475,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
         <v>143</v>
       </c>
@@ -4525,7 +4489,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="187" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="27">
         <v>5</v>
       </c>
@@ -4536,7 +4500,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="119" x14ac:dyDescent="0.2">
       <c r="B12" s="27">
         <v>7</v>
       </c>
@@ -4550,4 +4514,543 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC26FBFD-AFA6-DF4E-A246-4409436B2AEE}">
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5" style="40" customWidth="1"/>
+    <col min="2" max="2" width="5" style="40" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="37" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="39" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" style="39" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="31" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="B1" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="36"/>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="42">
+        <v>1</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="45" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="B4" s="42">
+        <f>B3+1</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="B5" s="42">
+        <f t="shared" ref="B5:B24" si="0">B4+1</f>
+        <v>3</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="42">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B7" s="42">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="B8" s="42">
+        <v>4.2</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="B9" s="42">
+        <v>4.2</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="42">
+        <v>4.2</v>
+      </c>
+      <c r="C10" s="43"/>
+      <c r="D10" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="42">
+        <f>B6+1</f>
+        <v>5</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B12" s="42">
+        <v>6.1</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="42">
+        <v>6.2</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="B14" s="42">
+        <f>B12+1</f>
+        <v>7.1</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="45"/>
+      <c r="E14" s="39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B15" s="42">
+        <v>7.2</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="42">
+        <v>7.2</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B17" s="42">
+        <f>B14+1</f>
+        <v>8.1</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="42">
+        <f t="shared" si="0"/>
+        <v>9.1</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B19" s="42">
+        <f t="shared" si="0"/>
+        <v>10.1</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B20" s="42">
+        <f t="shared" si="0"/>
+        <v>11.1</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="49"/>
+      <c r="E20" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="B22" s="42">
+        <f>B20+1</f>
+        <v>12.1</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="42">
+        <f t="shared" si="0"/>
+        <v>13.1</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="42">
+        <f t="shared" si="0"/>
+        <v>14.1</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="45"/>
+      <c r="E24" s="39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B25" s="42">
+        <v>14.2</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="42">
+        <v>14.3</v>
+      </c>
+      <c r="C26" s="43"/>
+      <c r="D26" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="42">
+        <v>14.4</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="A28" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="42">
+        <v>1</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B29" s="42">
+        <f t="shared" ref="B29:B35" si="1">B28+1</f>
+        <v>2</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="42">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="B31" s="42">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="B32" s="42">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="B33" s="42">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="B34" s="42">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B35" s="42">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C35" s="43"/>
+      <c r="E35" s="39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="B36" s="42">
+        <v>9.1</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="45"/>
+      <c r="E36" s="39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B37" s="42">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E37" s="39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B38" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="C38" s="43"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="B39" s="42">
+        <f>B36+1</f>
+        <v>10.1</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="42"/>
+      <c r="C40" s="43"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C41" s="39"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C42" s="43"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C43" s="43"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C44" s="43"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>